--- a/tools/test/fixtures/nha-ma-ba-ria.xlsx
+++ b/tools/test/fixtures/nha-ma-ba-ria.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>🏗 SETUP LẮP ĐẶT: NHÀ MA BÀ RỊA</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Tủ Điện 24 tép</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -51,6 +54,8 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
       <c r="C2">
         <v>760127194</v>
       </c>
@@ -90,7 +95,7 @@
         <v>4800000</v>
       </c>
       <c r="C5">
-        <v>2405000</v>
+        <v>2405000.0000000005</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -99,7 +104,7 @@
         <v>2405000</v>
       </c>
       <c r="F5">
-        <v>2405000</v>
+        <v>2405000.0000000005</v>
       </c>
     </row>
     <row r="6">
@@ -110,7 +115,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>825000</v>
+        <v>825000.0000000001</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -119,10 +124,370 @@
         <v>825000</v>
       </c>
       <c r="F6">
-        <v>825000</v>
+        <v>825000.0000000001</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="1">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="1">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/tools/test/fixtures/nha-ma-ba-ria.xlsx
+++ b/tools/test/fixtures/nha-ma-ba-ria.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>🏗 SETUP LẮP ĐẶT: NHÀ MA BÀ RỊA</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Thi công hệ vách (trọn gói)</t>
   </si>
 </sst>
 </file>
@@ -130,13 +133,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v/>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>5.4925668E8</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>5.4925668E8</v>
+      </c>
+      <c r="F7">
+        <v>5.4925668E8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1">
@@ -490,6 +507,15 @@
         <v/>
       </c>
     </row>
+    <row r="47" s="3" customFormat="1">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>